--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104559_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104559_W12.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4648</v>
+        <v>2.8201</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1918</v>
+        <v>2.6073</v>
       </c>
       <c r="F2" t="n">
-        <v>0.273</v>
+        <v>0.2128</v>
       </c>
       <c r="G2" t="n">
-        <v>2.832</v>
+        <v>2.8165</v>
       </c>
       <c r="H2" t="n">
-        <v>3.104</v>
+        <v>3.0938</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2719</v>
+        <v>-0.2773</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4754</v>
+        <v>4.4343</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9238</v>
+        <v>3.8988</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5516</v>
+        <v>0.5355</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6434</v>
+        <v>-1.6179</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5526</v>
+        <v>-0.1754</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.747</v>
+        <v>-0.2744</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1945</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>J. SORIANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4321</v>
+        <v>0.4952</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.2093</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.39</v>
+        <v>0.2859</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.362</v>
+        <v>0.4081</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1976</v>
+        <v>0.0922</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.1644</v>
+        <v>0.3159</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7504</v>
+        <v>0.279</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7477</v>
+        <v>0.279</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.4981</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6116</v>
+        <v>0.129</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9453</v>
+        <v>-0.1868</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6663</v>
+        <v>0.3159</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1531</v>
+        <v>0.0871</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0657</v>
+        <v>-0.0697</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.1568</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8678</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8678</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SORIANO</t>
+          <t>C. KOUMADJE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4058</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2177</v>
+        <v>0.8565</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1881</v>
+        <v>-0.7637</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4128</v>
+        <v>0.6621</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0982</v>
+        <v>1.344</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3145</v>
+        <v>-0.6819</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2873</v>
+        <v>1.5051</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2873</v>
+        <v>1.4307</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.0745</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1255</v>
+        <v>-0.843</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1891</v>
+        <v>-0.0866</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3145</v>
+        <v>-0.7563</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.007</v>
+        <v>-1.0034</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0696</v>
+        <v>-0.5089</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0626</v>
+        <v>-0.4945</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2833</v>
+        <v>-0.4659</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5998</v>
+        <v>-0.3481</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3165</v>
+        <v>-0.1177</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3123</v>
+        <v>0.3216</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6393</v>
+        <v>-0.635</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9516</v>
+        <v>0.9566</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6663</v>
+        <v>0.6647</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.354</v>
+        <v>-0.3432</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7086</v>
+        <v>-0.7039</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1051</v>
+        <v>0.3507</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2945</v>
+        <v>0.3529</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1893</v>
+        <v>-0.0022</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. KOUMADJE</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.6031</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7536</v>
+        <v>-0.2699</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8531</v>
+        <v>-0.3332</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6516</v>
+        <v>-2.3633</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3419</v>
+        <v>-0.2036</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6903</v>
+        <v>-2.1597</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5119</v>
+        <v>-0.7744</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4373</v>
+        <v>0.7305</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>-1.5048</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8603</v>
+        <v>-1.589</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0954</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7649</v>
+        <v>-0.6549</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1801</v>
+        <v>1.1276</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6261</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5541</v>
+        <v>0.1176</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0.8603</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3214</v>
+        <v>0.8603</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2729</v>
+        <v>-1.0244</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4188</v>
+        <v>-0.0823</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8542</v>
+        <v>-0.9421</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3414</v>
+        <v>-1.0757</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1181</v>
+        <v>-0.675</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2233</v>
+        <v>-0.4006</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2291</v>
+        <v>1.3302</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0799</v>
+        <v>1.2788</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1493</v>
+        <v>0.0515</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5706</v>
+        <v>-2.4059</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.198</v>
+        <v>-1.9538</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3726</v>
+        <v>-0.4521</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4952</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0931</v>
+        <v>0.5552</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2208</v>
+        <v>0.0019</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3139</v>
+        <v>0.5532</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9320000000000001</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4855</v>
+        <v>-1.5163</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6341</v>
+        <v>-0.4583</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8514</v>
+        <v>-1.058</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0793</v>
+        <v>-1.3372</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6768</v>
+        <v>-0.1314</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4025</v>
+        <v>-1.2058</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3582</v>
+        <v>1.1962</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2917</v>
+        <v>1.0472</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0665</v>
+        <v>0.1489</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4374</v>
+        <v>-2.5334</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.9684</v>
+        <v>-1.1786</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.469</v>
+        <v>-1.3548</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4952</v>
+        <v>-1.5934</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>2.5039</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08890000000000001</v>
+        <v>-0.1579</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5898</v>
+        <v>-0.2189</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6787</v>
+        <v>0.0609</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>-0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2685</v>
+        <v>-1.8279</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2765</v>
+        <v>-1.0563</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.992</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4399</v>
+        <v>-0.418</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0607</v>
+        <v>-2.0512</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6207</v>
+        <v>1.6332</v>
       </c>
       <c r="J9" t="n">
-        <v>1.267</v>
+        <v>1.2576</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0764</v>
+        <v>-0.0829</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3434</v>
+        <v>1.3405</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.707</v>
+        <v>-1.6756</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9843</v>
+        <v>-1.9683</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2773</v>
+        <v>0.2926</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6944</v>
+        <v>-0.2717</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7289</v>
+        <v>-0.4928</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0345</v>
+        <v>0.2211</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0241</v>
+        <v>-3.0073</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0573</v>
+        <v>-2.7174</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0333</v>
+        <v>-0.2899</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5597</v>
+        <v>-0.5543</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8744</v>
+        <v>0.8786</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.434</v>
+        <v>-1.433</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.163</v>
+        <v>-0.1691</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6234</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3967</v>
+        <v>-0.3852</v>
       </c>
       <c r="N10" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3717</v>
+        <v>-0.3635</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3992</v>
+        <v>-0.0444</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0275</v>
+        <v>-0.3191</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.552</v>
+        <v>-5.0835</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0159</v>
+        <v>-2.698</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5361</v>
+        <v>-2.3855</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2231</v>
+        <v>-2.231</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8339</v>
+        <v>-1.8406</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3892</v>
+        <v>-0.3903</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.7129</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9045</v>
+        <v>-0.921</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2185</v>
+        <v>0.2081</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5371</v>
+        <v>-1.518</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4216</v>
+        <v>0.058</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3811</v>
+        <v>-0.0258</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0405</v>
+        <v>0.0838</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.027</v>
+        <v>-6.0367</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.4278</v>
+        <v>-5.6119</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5992</v>
+        <v>-0.4248</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.2282</v>
+        <v>-3.235</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2264</v>
+        <v>-1.2345</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0018</v>
+        <v>-2.0005</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5185</v>
+        <v>-1.5623</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2016</v>
+        <v>-0.2283</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3169</v>
+        <v>-1.334</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7097</v>
+        <v>-1.6728</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0248</v>
+        <v>-1.0062</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6849</v>
+        <v>-0.6665</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.3098</v>
+        <v>-4.325</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2129</v>
+        <v>-0.2067</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.1979</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1313</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.1435</v>
+        <v>-16.157</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.2454</v>
+        <v>-9.569100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.898099999999999</v>
+        <v>-6.5879</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.024900000000001</v>
+        <v>-7.0062</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3343</v>
+        <v>-1.3627</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.6906</v>
+        <v>-5.6434</v>
       </c>
       <c r="J13" t="n">
-        <v>7.677299999999999</v>
+        <v>7.448400000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>8.277899999999999</v>
+        <v>8.122199999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6004000000000002</v>
+        <v>-0.6735999999999998</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.7023</v>
+        <v>-14.455</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.612099999999998</v>
+        <v>-9.4847</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.0903</v>
+        <v>-4.9699</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.8051</v>
+        <v>-6.8291</v>
       </c>
       <c r="Q13" t="n">
-        <v>-21.5493</v>
+        <v>-21.6249</v>
       </c>
       <c r="R13" t="n">
-        <v>14.7442</v>
+        <v>14.796</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.999999999990572e-05</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4838999999999999</v>
+        <v>-0.468</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4839</v>
+        <v>0.4679000000000002</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.3137</v>
+        <v>-2.3217</v>
       </c>
       <c r="W13" t="n">
-        <v>5.1101</v>
+        <v>5.075299999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.4238</v>
+        <v>-7.397</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.8823</v>
+        <v>7.6709</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5171</v>
+        <v>5.2423</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3652</v>
+        <v>2.4287</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3568</v>
+        <v>1.3445</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0721</v>
+        <v>0.0745</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2847</v>
+        <v>1.27</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4084</v>
+        <v>2.3784</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2224</v>
+        <v>1.2098</v>
       </c>
       <c r="L14" t="n">
-        <v>1.186</v>
+        <v>1.1686</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0516</v>
+        <v>-1.0339</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O14" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2326</v>
+        <v>0.0289</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1693</v>
+        <v>-0.4046</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4019</v>
+        <v>0.4335</v>
       </c>
       <c r="V14" t="n">
-        <v>3.1173</v>
+        <v>3.1107</v>
       </c>
       <c r="W14" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1355</v>
+        <v>5.0772</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2826</v>
+        <v>1.9037</v>
       </c>
       <c r="F15" t="n">
-        <v>3.8529</v>
+        <v>3.1736</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1549</v>
+        <v>-0.1437</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8559</v>
+        <v>-0.8423</v>
       </c>
       <c r="I15" t="n">
-        <v>0.701</v>
+        <v>0.6985</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0863</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3188</v>
+        <v>-0.3242</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4051</v>
+        <v>0.3943</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2411</v>
+        <v>-0.2138</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5371</v>
+        <v>-0.518</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5853</v>
+        <v>1.5169</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8257</v>
+        <v>0.4757</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7596</v>
+        <v>1.0412</v>
       </c>
       <c r="V15" t="n">
-        <v>2.571</v>
+        <v>2.5659</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9283</v>
+        <v>4.8314</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6667</v>
+        <v>2.874</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2616</v>
+        <v>1.9574</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9189</v>
+        <v>2.9163</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8238</v>
+        <v>0.8297</v>
       </c>
       <c r="I16" t="n">
-        <v>2.095</v>
+        <v>2.0866</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8723</v>
+        <v>2.8418</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0146</v>
+        <v>1.003</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8577</v>
+        <v>1.8388</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0466</v>
+        <v>0.0745</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2589</v>
+        <v>0.6388</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0212</v>
+        <v>0.2598</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2801</v>
+        <v>0.379</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2037</v>
+        <v>3.7768</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2278</v>
+        <v>3.4271</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0241</v>
+        <v>0.3497</v>
       </c>
       <c r="G17" t="n">
-        <v>5.0619</v>
+        <v>5.0509</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9481</v>
+        <v>2.9387</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1138</v>
+        <v>2.1122</v>
       </c>
       <c r="J17" t="n">
-        <v>5.1967</v>
+        <v>5.1648</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5948</v>
+        <v>3.5713</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1348</v>
+        <v>-0.1139</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2192</v>
+        <v>-0.6399</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8347</v>
+        <v>-0.5995</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3844</v>
+        <v>-0.0403</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>E. BROOKS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3951</v>
+        <v>1.5814</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7334</v>
+        <v>-1.6908</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3383</v>
+        <v>3.2721</v>
       </c>
       <c r="G18" t="n">
-        <v>0.09859999999999999</v>
+        <v>1.4107</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1573</v>
+        <v>1.1577</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0586</v>
+        <v>0.253</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.6521</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.4889</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.1632</v>
       </c>
       <c r="M18" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.2414</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1573</v>
+        <v>-0.3312</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0586</v>
+        <v>0.0898</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.1868</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4572</v>
+        <v>0.626</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5727</v>
+        <v>0.2993</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1155</v>
+        <v>0.3267</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1884</v>
+        <v>1.2095</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9091</v>
+        <v>0.5441</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2793</v>
+        <v>0.6654</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4315</v>
+        <v>-1.4153</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8718</v>
+        <v>-0.8567</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5598</v>
+        <v>-0.5586</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9873</v>
+        <v>0.979</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4676</v>
+        <v>0.4654</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4188</v>
+        <v>-2.3943</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P19" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.395</v>
+        <v>-0.4043</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2389</v>
+        <v>-0.5927</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1561</v>
+        <v>0.1884</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. BROOKS</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0013</v>
+        <v>0.7589</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7627</v>
+        <v>1.0264</v>
       </c>
       <c r="F20" t="n">
-        <v>2.764</v>
+        <v>-0.2675</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4202</v>
+        <v>0.1014</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1616</v>
+        <v>0.1579</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2585</v>
+        <v>-0.0565</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6881</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5097</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1785</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.268</v>
+        <v>0.1014</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.348</v>
+        <v>0.1579</v>
       </c>
       <c r="O20" t="n">
-        <v>0.08</v>
+        <v>-0.0565</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6293</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1757</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0348</v>
+        <v>0.8152</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1785</v>
+        <v>0.8686</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1437</v>
+        <v>-0.0534</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0399</v>
+        <v>-0.1125</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1023</v>
+        <v>-0.4815</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0624</v>
+        <v>0.369</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3121</v>
+        <v>2.3122</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0735</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3857</v>
+        <v>2.3895</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7275</v>
+        <v>1.709</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3841</v>
+        <v>0.3685</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3434</v>
+        <v>1.3405</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5847</v>
+        <v>0.6032</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1697</v>
+        <v>0.0988</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4386</v>
+        <v>0.0858</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2689</v>
+        <v>0.013</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="22">
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2152,13 +2152,13 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9026</v>
+        <v>-0.3441</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2552</v>
+        <v>-0.3661</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6474</v>
+        <v>0.0219</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2649</v>
+        <v>-0.278</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8832</v>
+        <v>-0.8791</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6183</v>
+        <v>0.601</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3298</v>
+        <v>1.2858</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0075</v>
+        <v>0.989</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3223</v>
+        <v>0.2968</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5947</v>
+        <v>-1.5638</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8906</v>
+        <v>-1.8681</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5697</v>
+        <v>0.0022</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1825</v>
+        <v>-0.2374</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3871</v>
+        <v>0.2396</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7605</v>
+        <v>-2.4597</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7764</v>
+        <v>-2.6687</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0159</v>
+        <v>0.209</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.6472</v>
+        <v>-1.6502</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7886</v>
+        <v>-1.7937</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0745</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.206</v>
+        <v>0.101</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1364</v>
+        <v>0.0523</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6722</v>
+        <v>-3.2492</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5418</v>
+        <v>-3.2225</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1304</v>
+        <v>-0.0267</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.4292</v>
+        <v>-2.428</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2857</v>
+        <v>-1.2839</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.1435</v>
+        <v>-1.144</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0213</v>
+        <v>-0.0469</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7304</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7517</v>
+        <v>-0.7601</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.4079</v>
+        <v>-2.3811</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.0161</v>
+        <v>-1.9971</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R25" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8308</v>
+        <v>-0.4147</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0253</v>
+        <v>-0.6717</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1945</v>
+        <v>0.257</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>16.1435</v>
+        <v>18.5262</v>
       </c>
       <c r="E26" t="n">
-        <v>6.898299999999997</v>
+        <v>6.587999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>9.245200000000001</v>
+        <v>11.9382</v>
       </c>
       <c r="G26" t="n">
-        <v>7.024899999999999</v>
+        <v>7.006399999999998</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3342</v>
+        <v>1.362699999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>5.6906</v>
+        <v>5.6436</v>
       </c>
       <c r="J26" t="n">
-        <v>14.7024</v>
+        <v>14.4547</v>
       </c>
       <c r="K26" t="n">
-        <v>9.612299999999999</v>
+        <v>9.484900000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>5.090199999999999</v>
+        <v>4.969899999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-7.6774</v>
+        <v>-7.448499999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-8.277799999999999</v>
+        <v>-8.1221</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6001000000000005</v>
+        <v>0.6737000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>6.8051</v>
+        <v>6.8289</v>
       </c>
       <c r="Q26" t="n">
-        <v>-14.7442</v>
+        <v>-14.796</v>
       </c>
       <c r="R26" t="n">
-        <v>21.5493</v>
+        <v>21.6248</v>
       </c>
       <c r="S26" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>2.3689</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4836000000000001</v>
+        <v>-0.468</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4838000000000002</v>
+        <v>2.837</v>
       </c>
       <c r="V26" t="n">
-        <v>2.3137</v>
+        <v>2.321800000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>7.4238</v>
+        <v>7.397200000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.110099999999999</v>
+        <v>-5.075299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104559_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104559_W12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.397</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104559_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-5.075299999999999</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
